--- a/Training/Day3_Calibration/matlab_pipeline/data/output/IO-2019_utilities_split.xlsx
+++ b/Training/Day3_Calibration/matlab_pipeline/data/output/IO-2019_utilities_split.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="IO_Split" sheetId="1" r:id="rId2"/>
+    <sheet name="IO_Split" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Sector</t>
   </si>
@@ -52,6 +53,21 @@
   </si>
   <si>
     <t>LAB</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>MiningEnergy</t>
+  </si>
+  <si>
+    <t>Refinery</t>
+  </si>
+  <si>
+    <t>Secondary</t>
+  </si>
+  <si>
+    <t>Tertiary</t>
   </si>
   <si>
     <t>CONS</t>
@@ -90,7 +106,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -128,28 +144,28 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="true"/>
+    <col min="1" max="1" width="12.37890625" customWidth="true"/>
     <col min="2" max="2" width="11.7109375" customWidth="true"/>
-    <col min="3" max="3" width="13.28515625" customWidth="true"/>
+    <col min="3" max="3" width="12.046875" customWidth="true"/>
     <col min="4" max="4" width="11.7109375" customWidth="true"/>
-    <col min="5" max="5" width="14.85546875" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" customWidth="true"/>
     <col min="6" max="6" width="11.7109375" customWidth="true"/>
     <col min="7" max="7" width="11.7109375" customWidth="true"/>
     <col min="8" max="8" width="11.7109375" customWidth="true"/>
     <col min="9" max="9" width="11.7109375" customWidth="true"/>
-    <col min="10" max="10" width="13.42578125" customWidth="true"/>
-    <col min="11" max="11" width="7.140625" customWidth="true"/>
-    <col min="12" max="12" width="14.5703125" customWidth="true"/>
+    <col min="10" max="10" width="13.37890625" customWidth="true"/>
+    <col min="11" max="11" width="6.7109375" customWidth="true"/>
+    <col min="12" max="12" width="13.82421875" customWidth="true"/>
     <col min="13" max="13" width="11.7109375" customWidth="true"/>
     <col min="14" max="14" width="11.7109375" customWidth="true"/>
-    <col min="15" max="15" width="14.85546875" customWidth="true"/>
-    <col min="16" max="16" width="14.140625" customWidth="true"/>
-    <col min="17" max="17" width="20" customWidth="true"/>
+    <col min="15" max="15" width="14.7109375" customWidth="true"/>
+    <col min="16" max="16" width="12.82421875" customWidth="true"/>
+    <col min="17" max="17" width="18.15625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -157,52 +173,52 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -231,7 +247,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="0">
-        <v>40393133.665032581</v>
+        <v>40393133.66503258</v>
       </c>
       <c r="J2" s="0">
         <v>56187432.569712847</v>
@@ -443,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="0">
-        <v>2181424571.5849567</v>
+        <v>2181424571.5849566</v>
       </c>
       <c r="J6" s="0">
         <v>62157624.271570027</v>
@@ -455,7 +471,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="0">
-        <v>5596994000.8707686</v>
+        <v>5596994000.8707685</v>
       </c>
       <c r="N6" s="0">
         <v>5207372374.951601</v>
@@ -570,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="0">
-        <v>3860257.5566352625</v>
+        <v>3860257.5566352624</v>
       </c>
       <c r="Q8" s="0">
         <v>1685936.1151140083</v>
@@ -623,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="0">
-        <v>3860257.5566352625</v>
+        <v>3860257.5566352624</v>
       </c>
       <c r="Q9" s="0">
         <v>1685936.1151140083</v>
